--- a/artfynd/A 63207-2019 artfynd.xlsx
+++ b/artfynd/A 63207-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63207-2019 artfynd.xlsx
+++ b/artfynd/A 63207-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7255,6 +7255,125 @@
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>118047793</v>
+      </c>
+      <c r="B56" t="n">
+        <v>97873</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Gammal åkerlycka i skogen S Furusjömåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>535927</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6332407</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Åseda</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Elin Åkelius</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Elin Åkelius</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63207-2019 artfynd.xlsx
+++ b/artfynd/A 63207-2019 artfynd.xlsx
@@ -7260,7 +7260,7 @@
         <v>118047793</v>
       </c>
       <c r="B56" t="n">
-        <v>97873</v>
+        <v>97875</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
